--- a/research/NYC_Reviewer_Additions.xlsx
+++ b/research/NYC_Reviewer_Additions.xlsx
@@ -20,7 +20,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Each row was checked against the organization's own website on the date in 'Last verified' before being added. Same columns and conventions as the main reference workbooks. Wording is chosen with the tagging rules in mind: '24/7' reads as an emergency vet and 'rabbit' as a domestic-rabbit rescue, so neither appears where it would mislead.</t>
+          <t xml:space="preserve">Each row was checked against the organization's own website on the date in 'Last verified' before being added, unless its notes say otherwise. Same columns and conventions as the main reference workbooks. Wording is chosen with the tagging rules in mind: '24/7' reads as an emergency vet, 'rabbit' as a domestic-rabbit rescue, and the words 'rescue' and 'rehabilitat' tag a row as one even inside 'not a rescue', so reporting lines avoid them.</t>
         </is>
       </c>
     </row>
@@ -174,72 +174,351 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SENIOR &amp; SPECIAL-NEEDS CATS - rescue, adoption and owner surrender (Manhattan)</t>
+          <t xml:space="preserve">WILDLIFE REHABILITATION - in the city (home-based rehabber, small mammals)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Island Wildlife Inc</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wildlife rescue and rehabilitation nonprofit (small mammals), home-based</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wild small mammals</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Bronx; New York City</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(914) 309-0279</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FB /islandwildlife</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A 501(c)(3) wildlife rescue and rehabilitator run from a home in the Bronx, which is normal for this kind of operation, so there is no public street address. Found by a reviewer on 2026-09-21. Its only public channel is Facebook, which cannot be read automatically, so nobody here has confirmed the number: confirm before relying on it, and try the DEC directory or the city's wildlife hospital if it does not answer.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.facebook.com/islandwildlife</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SENIOR &amp; SPECIAL-NEEDS CATS - rescue, adoption and owner surrender (Manhattan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Frankie's Feline Fund</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t xml:space="preserve">Rescue / adoption (foster-based; senior and special-needs cats; owner surrenders)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">Cats - elderly and special-needs</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">Manhattan (Upper East Side / Upper West Side); foster-based, no shelter building</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t xml:space="preserve">917-514-0228</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">frankiesfelinefund@gmail.com</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">https://frankiesfelinefund.org</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">Email frankiesfelinefund@gmail.com or call 917-514-0228</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve">FB /frankiesfelinefund</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">All-volunteer 501(c)(3) rescuing abandoned elderly and special-needs cats. Adoption ($75 fee) and a senior-to-senior foster programme. Accepts owner surrenders of senior cats to keep them out of the shelter system. A different organization from Frankie's Friends, which helps pay vet bills.</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">https://frankiesfelinefund.org</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WILDLIFE REPORTING LINES - who to call about sick, dead, stranded or illegally kept wildlife. Reporting lines only: for a live injured animal use the wildlife carers above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NYS DEC Region 2 (New York City office)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State environmental agency, New York City regional office - large mammals, deer, wildlife questions, referrals to licensed wildlife carers; a government office that does not collect animals</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wildlife, including large mammals and deer</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All five boroughs (Brooklyn, Bronx, Manhattan, Queens and Staten Island)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11101</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(718) 482-4900 (daytime, Mon-Fri 8:30am-4:45pm); 1-844-332-3267 (DEC dispatch, after hours)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dec.ny.gov</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The DEC office that covers the five boroughs, at 1 Hunters Point Plaza, 47-40 21st Street, Long Island City, NY 11101. Call in the daytime about deer, coyotes and other large animals, wildlife you think is being kept or hunted illegally, or to be pointed to a licensed wildlife carer. After hours the DEC dispatch line takes wildlife calls statewide. A reporting and referral line: they will not collect an injured bird.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dec.ny.gov/about/contact-us/statewide-office-information</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOAA Greater Atlantic marine mammal and sea turtle stranding hotline</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">National reporting hotline for stranded, injured, entangled or dead seals, whales, dolphins and sea turtles; backup to the New York stranding line listed above</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seals, whales, dolphins, porpoises, sea turtles</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">National hotline; use from anywhere on the coast</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(866) 755-6622</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.fisheries.noaa.gov/report</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOAA's stranding and entanglement hotline for the Greater Atlantic region, Maine to Virginia, which includes every New York City beach. Call it if the New York stranding line does not answer. Keep people and pets well away from the animal and do not push it back into the water; a seal resting on a beach is often healthy.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.fisheries.noaa.gov/report</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USDA Report Sick Birds line</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Federal reporting line for sick or dead birds, run for avian influenza surveillance; a reporting line that does not collect animals</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Birds - poultry, backyard flocks, and sick or dead wild birds</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">National hotline; use from anywhere</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(866) 536-7593</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aphis.usda.gov/livestock-poultry-disease/avian/defend-the-flock</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USDA's Report Sick Birds line, run for poultry and backyard flocks; it also takes reports of sick or dead wild birds and routes them to the right agency. For a live injured bird call the city's wildlife hospital instead. Do not touch dead birds with bare hands; in the city you can also report dead birds to 311.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aphis.usda.gov/sites/default/files/card-report-sick-birds.pdf</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USFWS wildlife crime tip line</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Federal law-enforcement tip line for suspected wildlife crime - trafficking, killing or selling protected species; a reporting line that does not collect animals</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wildlife</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">National hotline; use from anywhere</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1-844-397-8477</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.fws.gov/story/how-report-wildlife-crime</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Online tip form: https://www.fws.gov/wildlife-crime-tips</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The U.S. Fish and Wildlife Service tip line (1-844-FWS-TIPS) for suspected wildlife crime: killing or trapping protected birds and animals, selling wildlife or wildlife parts, or crimes on federal refuges. Reports can be anonymous. For cruelty to a pet or ordinary animal in New York City call 311 or 911 instead; for hunting or fishing violations off federal land, DEC Region 2.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.fws.gov/story/how-report-wildlife-crime</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-22</t>
         </is>
